--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>392</v>
+      </c>
+      <c r="E2">
         <v>6</v>
       </c>
-      <c r="D2">
-        <v>399</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="G2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D3">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H3">
         <v>426</v>
